--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/3008-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/3008-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E525FC49-3C53-4CEB-97F3-A3D939C854D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A58AF06F-891E-4390-A3C5-88B801A8DA6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{1FF62E97-A2ED-473B-893E-DC9EFA13FD55}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{C93C8E4E-41F3-4B02-ACC6-1867A53114F8}"/>
   </bookViews>
   <sheets>
     <sheet name="3008-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1537,23 +1537,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADC44E57-81AC-4F45-8400-8A78483E9555}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BF3AB0F-2B30-407A-BC06-407345C888F0}">
   <dimension ref="A1:R43"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -1581,7 +1581,7 @@
       <c r="Q1" s="34"/>
       <c r="R1" s="26"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
         <v>1</v>
       </c>
@@ -1611,7 +1611,7 @@
       <c r="Q2" s="36"/>
       <c r="R2" s="37"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
         <v>2</v>
       </c>
@@ -1657,7 +1657,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="29"/>
       <c r="B4" s="30"/>
       <c r="C4" s="7"/>
@@ -1707,7 +1707,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="41">
         <v>2026</v>
       </c>
@@ -1761,7 +1761,7 @@
         <v>4.3099999999999996</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="43"/>
       <c r="B6" s="44"/>
       <c r="C6" s="46"/>
@@ -1787,7 +1787,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
@@ -1843,7 +1843,7 @@
         <v>2.15</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="51">
         <v>2025</v>
       </c>
@@ -1897,7 +1897,7 @@
         <v>3.43</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>27</v>
       </c>
@@ -1953,7 +1953,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -2009,7 +2009,7 @@
         <v>2.2799999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="53">
         <v>2024</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>27</v>
       </c>
@@ -2119,7 +2119,7 @@
         <v>1.41</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>27</v>
       </c>
@@ -2175,7 +2175,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="51">
         <v>2023</v>
       </c>
@@ -2229,7 +2229,7 @@
         <v>3.29</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>27</v>
       </c>
@@ -2285,7 +2285,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>27</v>
       </c>
@@ -2341,7 +2341,7 @@
         <v>1.99</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="53">
         <v>2022</v>
       </c>
@@ -2395,7 +2395,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>27</v>
       </c>
@@ -2451,7 +2451,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>27</v>
       </c>
@@ -2507,7 +2507,7 @@
         <v>1.94</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>27</v>
       </c>
@@ -2563,7 +2563,7 @@
         <v>1.26</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="51">
         <v>2021</v>
       </c>
@@ -2617,7 +2617,7 @@
         <v>3.24</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="53">
         <v>2020</v>
       </c>
@@ -2671,7 +2671,7 @@
         <v>1.98</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="51">
         <v>2019</v>
       </c>
@@ -2725,7 +2725,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="53">
         <v>2018</v>
       </c>
@@ -2779,7 +2779,7 @@
         <v>1.63</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="51">
         <v>2017</v>
       </c>
@@ -2833,7 +2833,7 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="53">
         <v>2016</v>
       </c>
@@ -2887,7 +2887,7 @@
         <v>1.68</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="51">
         <v>2015</v>
       </c>
@@ -2941,7 +2941,7 @@
         <v>1.72</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="53">
         <v>2014</v>
       </c>
@@ -2995,7 +2995,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="51">
         <v>2013</v>
       </c>
@@ -3049,7 +3049,7 @@
         <v>1.57</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="53">
         <v>2012</v>
       </c>
@@ -3103,7 +3103,7 @@
         <v>2.84</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="51">
         <v>2011</v>
       </c>
@@ -3157,7 +3157,7 @@
         <v>1.37</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="53">
         <v>2010</v>
       </c>
@@ -3211,7 +3211,7 @@
         <v>1.63</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="51">
         <v>2009</v>
       </c>
@@ -3265,7 +3265,7 @@
         <v>2.4900000000000002</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="53">
         <v>2008</v>
       </c>
@@ -3319,7 +3319,7 @@
         <v>2.16</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="51">
         <v>2007</v>
       </c>
@@ -3373,7 +3373,7 @@
         <v>2.94</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="53">
         <v>2006</v>
       </c>
@@ -3427,7 +3427,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="51">
         <v>2005</v>
       </c>
@@ -3481,7 +3481,7 @@
         <v>1.88</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="53">
         <v>2004</v>
       </c>
@@ -3535,7 +3535,7 @@
         <v>3.14</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="51">
         <v>2003</v>
       </c>
@@ -3589,7 +3589,7 @@
         <v>2.63</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="53">
         <v>2002</v>
       </c>
@@ -3643,7 +3643,7 @@
         <v>2.63</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="51">
         <v>2001</v>
       </c>
@@ -3697,7 +3697,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="53">
         <v>2000</v>
       </c>
@@ -3751,7 +3751,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="51" t="s">
         <v>48</v>
       </c>
